--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-30.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-30.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/metodos_aprovados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="11_24C55084542AB6638F3A2311595ED87656CDEBE9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69E69EA7-A0D1-4216-AC6C-D7FE331DB5F0}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="11_24C55084542AB6638F3A2311595ED87656CDEBE9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B397651-6D44-4FB1-9307-3AA407C3BC2D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1880,11 +1880,11 @@
         <v>21</v>
       </c>
       <c r="N25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25">
         <f t="shared" si="0"/>
-        <v>0.15439999999999998</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
@@ -1928,11 +1928,11 @@
         <v>25</v>
       </c>
       <c r="N26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26">
         <f t="shared" si="0"/>
-        <v>3.932355338223309E-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-30.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-30.xlsx
@@ -1324,12 +1324,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>3x1</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1342,10 +1342,10 @@
         <v>200</v>
       </c>
       <c r="K15" t="n">
-        <v>51.07</v>
+        <v>-200</v>
       </c>
       <c r="L15" t="n">
-        <v>0.955</v>
+        <v>-3.74</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>1.4</v>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-30.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-30.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/metodos_aprovados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_2EA96AAC1858120E62355476585DCE3A8747EA03" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F303D08E-B069-4206-9AB9-BD5D32A6CD3E}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_2EA96AAC1858120E62355476585DCE3A8747EA03" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87A8DABD-3DBB-4CE4-BB48-6A592A0C598F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -320,6 +320,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -705,8 +709,8 @@
         <v>1</v>
       </c>
       <c r="O2">
-        <f>IF(N2=1,0.965/(J2-1),-1)</f>
-        <v>4.8492462311557783E-3</v>
+        <f>IF(N2=1,0.965/(E2-1),-1)</f>
+        <v>0.21636771300448429</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -753,7 +757,7 @@
         <v>0</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O16" si="0">IF(N3=1,0.965/(J3-1),-1)</f>
+        <f t="shared" ref="O3:O16" si="0">IF(N3=1,0.965/(E3-1),-1)</f>
         <v>-1</v>
       </c>
     </row>
@@ -802,7 +806,7 @@
       </c>
       <c r="O4">
         <f t="shared" si="0"/>
-        <v>4.8492462311557783E-3</v>
+        <v>0.16637931034482759</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
@@ -850,7 +854,7 @@
       </c>
       <c r="O5">
         <f t="shared" si="0"/>
-        <v>4.8492462311557783E-3</v>
+        <v>0.19416498993963782</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
@@ -898,7 +902,7 @@
       </c>
       <c r="O6">
         <f t="shared" si="0"/>
-        <v>4.8492462311557783E-3</v>
+        <v>0.16637931034482759</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -946,7 +950,7 @@
       </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>4.8492462311557783E-3</v>
+        <v>0.17262969588550983</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
@@ -994,7 +998,7 @@
       </c>
       <c r="O8">
         <f t="shared" si="0"/>
-        <v>4.8492462311557783E-3</v>
+        <v>0.19815195071868583</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
@@ -1042,7 +1046,7 @@
       </c>
       <c r="O9">
         <f t="shared" si="0"/>
-        <v>4.8492462311557783E-3</v>
+        <v>0.19815195071868583</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
@@ -1090,7 +1094,7 @@
       </c>
       <c r="O10">
         <f t="shared" si="0"/>
-        <v>4.8492462311557783E-3</v>
+        <v>7.4230769230769225E-2</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
@@ -1138,7 +1142,7 @@
       </c>
       <c r="O11">
         <f t="shared" si="0"/>
-        <v>4.8492462311557783E-3</v>
+        <v>0.11668681983071343</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
@@ -1186,7 +1190,7 @@
       </c>
       <c r="O12">
         <f t="shared" si="0"/>
-        <v>4.8492462311557783E-3</v>
+        <v>7.4230769230769225E-2</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
@@ -1234,7 +1238,7 @@
       </c>
       <c r="O13">
         <f t="shared" si="0"/>
-        <v>4.8492462311557783E-3</v>
+        <v>0.20230607966457023</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
@@ -1282,7 +1286,7 @@
       </c>
       <c r="O14">
         <f t="shared" si="0"/>
-        <v>4.8492462311557783E-3</v>
+        <v>0.11668681983071343</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
@@ -1378,7 +1382,7 @@
       </c>
       <c r="O16">
         <f t="shared" si="0"/>
-        <v>4.8492462311557783E-3</v>
+        <v>0.1790352504638219</v>
       </c>
     </row>
   </sheetData>
